--- a/model_summary.xlsx
+++ b/model_summary.xlsx
@@ -450,10 +450,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>643.9775506283405</v>
+        <v>629.6244910605436</v>
       </c>
       <c r="C2" t="n">
-        <v>235.9483443707058</v>
+        <v>234.8547152542374</v>
       </c>
     </row>
   </sheetData>

--- a/model_summary.xlsx
+++ b/model_summary.xlsx
@@ -436,12 +436,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>max_distance_km</t>
+          <t>max_store_distance_km</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>avg_distance_km</t>
+          <t>avg_store_distance_km</t>
         </is>
       </c>
     </row>

--- a/model_summary.xlsx
+++ b/model_summary.xlsx
@@ -431,17 +431,17 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>optimal_k</t>
+          <t>Optimal_K</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>max_store_distance_km</t>
+          <t>Max_Distance_km</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>avg_store_distance_km</t>
+          <t>Avg_Distance_km</t>
         </is>
       </c>
     </row>

--- a/model_summary.xlsx
+++ b/model_summary.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Optimal_K</t>
+          <t>Fixed_K</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -447,13 +447,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>629.6244910605436</v>
+        <v>1203.997132895375</v>
       </c>
       <c r="C2" t="n">
-        <v>234.8547152542374</v>
+        <v>341.2426941487563</v>
       </c>
     </row>
   </sheetData>
